--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,346 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>23:25:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>23:28:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10:29:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10:31:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10:35:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10:44:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>19:49:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:51:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:03:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21:09:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>21:12:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>08:52:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>08:58:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>08:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>09:30:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10:09:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>13:32:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>66704151_MIn</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13:33:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>66713643_Sky</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>14:13:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>66704151_MIn</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>14:14:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
